--- a/Shallow learners/LightGBM/LightGBM_uni_param_search.xlsx
+++ b/Shallow learners/LightGBM/LightGBM_uni_param_search.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/59168efb92a48cee/Delt skrivebord/Data Science/Speciale/Energinet/Delte scripts/Speciale_Kode/Shallow learners/LightGBM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_AD4D1D646341095ACB7000E1DD96DCAA683EDF1E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62B45EFF-1FB1-4852-94CC-397B7E7DC1D1}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="11_AD4D1D646341095ACB7000E1DD96DCAA683EDF1E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DC28110-86C3-40BF-AAFF-06EA4615C637}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15855" yWindow="30" windowWidth="12495" windowHeight="15450" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LightGBM_uni_DK1_param_search_r" sheetId="2" r:id="rId1"/>
@@ -19,10 +19,21 @@
   <definedNames>
     <definedName name="EksterneData_1" localSheetId="0" hidden="1">LightGBM_uni_DK1_param_search_r!$A$1:$Z$109</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -153,9 +164,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -179,6 +189,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -653,10 +667,10 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" s="2">
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="1">
         <v>45292</v>
       </c>
       <c r="M2">
@@ -733,10 +747,10 @@
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3" s="2">
+      <c r="K3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="1">
         <v>45292</v>
       </c>
       <c r="M3">
@@ -813,10 +827,10 @@
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4" s="2">
+      <c r="K4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" s="1">
         <v>45292</v>
       </c>
       <c r="M4">
@@ -893,10 +907,10 @@
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" s="2">
+      <c r="K5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" s="1">
         <v>45292</v>
       </c>
       <c r="M5">
@@ -973,10 +987,10 @@
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6" s="2">
+      <c r="K6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6" s="1">
         <v>45292</v>
       </c>
       <c r="M6">
@@ -1053,10 +1067,10 @@
       <c r="J7">
         <v>0</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L7" s="2">
+      <c r="K7" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="1">
         <v>45292</v>
       </c>
       <c r="M7">
@@ -1133,10 +1147,10 @@
       <c r="J8">
         <v>0</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L8" s="2">
+      <c r="K8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" s="1">
         <v>45292</v>
       </c>
       <c r="M8">
@@ -1213,10 +1227,10 @@
       <c r="J9">
         <v>0</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L9" s="2">
+      <c r="K9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L9" s="1">
         <v>45292</v>
       </c>
       <c r="M9">
@@ -1293,10 +1307,10 @@
       <c r="J10">
         <v>0</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L10" s="2">
+      <c r="K10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L10" s="1">
         <v>45292</v>
       </c>
       <c r="M10">
@@ -1373,10 +1387,10 @@
       <c r="J11">
         <v>0</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" s="2">
+      <c r="K11" t="s">
+        <v>26</v>
+      </c>
+      <c r="L11" s="1">
         <v>45292</v>
       </c>
       <c r="M11">
@@ -1453,10 +1467,10 @@
       <c r="J12">
         <v>0</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L12" s="2">
+      <c r="K12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L12" s="1">
         <v>45292</v>
       </c>
       <c r="M12">
@@ -1533,10 +1547,10 @@
       <c r="J13">
         <v>0</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L13" s="2">
+      <c r="K13" t="s">
+        <v>26</v>
+      </c>
+      <c r="L13" s="1">
         <v>45292</v>
       </c>
       <c r="M13">
@@ -1613,10 +1627,10 @@
       <c r="J14">
         <v>0</v>
       </c>
-      <c r="K14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L14" s="2">
+      <c r="K14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" s="1">
         <v>45292</v>
       </c>
       <c r="M14">
@@ -1693,10 +1707,10 @@
       <c r="J15">
         <v>0</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" s="2">
+      <c r="K15" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" s="1">
         <v>45292</v>
       </c>
       <c r="M15">
@@ -1773,10 +1787,10 @@
       <c r="J16">
         <v>0</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L16" s="2">
+      <c r="K16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L16" s="1">
         <v>45292</v>
       </c>
       <c r="M16">
@@ -1853,10 +1867,10 @@
       <c r="J17">
         <v>0</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L17" s="2">
+      <c r="K17" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" s="1">
         <v>45292</v>
       </c>
       <c r="M17">
@@ -1933,10 +1947,10 @@
       <c r="J18">
         <v>0</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L18" s="2">
+      <c r="K18" t="s">
+        <v>26</v>
+      </c>
+      <c r="L18" s="1">
         <v>45292</v>
       </c>
       <c r="M18">
@@ -2013,10 +2027,10 @@
       <c r="J19">
         <v>0</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L19" s="2">
+      <c r="K19" t="s">
+        <v>26</v>
+      </c>
+      <c r="L19" s="1">
         <v>45292</v>
       </c>
       <c r="M19">
@@ -2093,10 +2107,10 @@
       <c r="J20">
         <v>0</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L20" s="2">
+      <c r="K20" t="s">
+        <v>26</v>
+      </c>
+      <c r="L20" s="1">
         <v>45292</v>
       </c>
       <c r="M20">
@@ -2173,10 +2187,10 @@
       <c r="J21">
         <v>0</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L21" s="2">
+      <c r="K21" t="s">
+        <v>26</v>
+      </c>
+      <c r="L21" s="1">
         <v>45292</v>
       </c>
       <c r="M21">
@@ -2253,10 +2267,10 @@
       <c r="J22">
         <v>0</v>
       </c>
-      <c r="K22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L22" s="2">
+      <c r="K22" t="s">
+        <v>26</v>
+      </c>
+      <c r="L22" s="1">
         <v>45292</v>
       </c>
       <c r="M22">
@@ -2333,10 +2347,10 @@
       <c r="J23">
         <v>0</v>
       </c>
-      <c r="K23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L23" s="2">
+      <c r="K23" t="s">
+        <v>26</v>
+      </c>
+      <c r="L23" s="1">
         <v>45292</v>
       </c>
       <c r="M23">
@@ -2413,10 +2427,10 @@
       <c r="J24">
         <v>0</v>
       </c>
-      <c r="K24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L24" s="2">
+      <c r="K24" t="s">
+        <v>26</v>
+      </c>
+      <c r="L24" s="1">
         <v>45292</v>
       </c>
       <c r="M24">
@@ -2493,10 +2507,10 @@
       <c r="J25">
         <v>0</v>
       </c>
-      <c r="K25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L25" s="2">
+      <c r="K25" t="s">
+        <v>26</v>
+      </c>
+      <c r="L25" s="1">
         <v>45292</v>
       </c>
       <c r="M25">
@@ -2573,10 +2587,10 @@
       <c r="J26">
         <v>0</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L26" s="2">
+      <c r="K26" t="s">
+        <v>26</v>
+      </c>
+      <c r="L26" s="1">
         <v>45292</v>
       </c>
       <c r="M26">
@@ -2653,10 +2667,10 @@
       <c r="J27">
         <v>0</v>
       </c>
-      <c r="K27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L27" s="2">
+      <c r="K27" t="s">
+        <v>26</v>
+      </c>
+      <c r="L27" s="1">
         <v>45292</v>
       </c>
       <c r="M27">
@@ -2733,10 +2747,10 @@
       <c r="J28">
         <v>0</v>
       </c>
-      <c r="K28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L28" s="2">
+      <c r="K28" t="s">
+        <v>26</v>
+      </c>
+      <c r="L28" s="1">
         <v>45292</v>
       </c>
       <c r="M28">
@@ -2813,10 +2827,10 @@
       <c r="J29">
         <v>0</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L29" s="2">
+      <c r="K29" t="s">
+        <v>26</v>
+      </c>
+      <c r="L29" s="1">
         <v>45292</v>
       </c>
       <c r="M29">
@@ -2893,10 +2907,10 @@
       <c r="J30">
         <v>0</v>
       </c>
-      <c r="K30" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L30" s="2">
+      <c r="K30" t="s">
+        <v>26</v>
+      </c>
+      <c r="L30" s="1">
         <v>45292</v>
       </c>
       <c r="M30">
@@ -2973,10 +2987,10 @@
       <c r="J31">
         <v>0</v>
       </c>
-      <c r="K31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L31" s="2">
+      <c r="K31" t="s">
+        <v>26</v>
+      </c>
+      <c r="L31" s="1">
         <v>45292</v>
       </c>
       <c r="M31">
@@ -3053,10 +3067,10 @@
       <c r="J32">
         <v>0</v>
       </c>
-      <c r="K32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L32" s="2">
+      <c r="K32" t="s">
+        <v>26</v>
+      </c>
+      <c r="L32" s="1">
         <v>45292</v>
       </c>
       <c r="M32">
@@ -3133,10 +3147,10 @@
       <c r="J33">
         <v>0</v>
       </c>
-      <c r="K33" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L33" s="2">
+      <c r="K33" t="s">
+        <v>26</v>
+      </c>
+      <c r="L33" s="1">
         <v>45292</v>
       </c>
       <c r="M33">
@@ -3213,10 +3227,10 @@
       <c r="J34">
         <v>0</v>
       </c>
-      <c r="K34" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L34" s="2">
+      <c r="K34" t="s">
+        <v>26</v>
+      </c>
+      <c r="L34" s="1">
         <v>45292</v>
       </c>
       <c r="M34">
@@ -3293,10 +3307,10 @@
       <c r="J35">
         <v>0</v>
       </c>
-      <c r="K35" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L35" s="2">
+      <c r="K35" t="s">
+        <v>26</v>
+      </c>
+      <c r="L35" s="1">
         <v>45292</v>
       </c>
       <c r="M35">
@@ -3373,10 +3387,10 @@
       <c r="J36">
         <v>0</v>
       </c>
-      <c r="K36" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L36" s="2">
+      <c r="K36" t="s">
+        <v>26</v>
+      </c>
+      <c r="L36" s="1">
         <v>45292</v>
       </c>
       <c r="M36">
@@ -3453,10 +3467,10 @@
       <c r="J37">
         <v>0</v>
       </c>
-      <c r="K37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L37" s="2">
+      <c r="K37" t="s">
+        <v>26</v>
+      </c>
+      <c r="L37" s="1">
         <v>45292</v>
       </c>
       <c r="M37">
@@ -3533,10 +3547,10 @@
       <c r="J38">
         <v>0</v>
       </c>
-      <c r="K38" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L38" s="2">
+      <c r="K38" t="s">
+        <v>26</v>
+      </c>
+      <c r="L38" s="1">
         <v>45292</v>
       </c>
       <c r="M38">
@@ -3613,10 +3627,10 @@
       <c r="J39">
         <v>0</v>
       </c>
-      <c r="K39" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L39" s="2">
+      <c r="K39" t="s">
+        <v>26</v>
+      </c>
+      <c r="L39" s="1">
         <v>45292</v>
       </c>
       <c r="M39">
@@ -3693,10 +3707,10 @@
       <c r="J40">
         <v>0</v>
       </c>
-      <c r="K40" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L40" s="2">
+      <c r="K40" t="s">
+        <v>26</v>
+      </c>
+      <c r="L40" s="1">
         <v>45292</v>
       </c>
       <c r="M40">
@@ -3773,10 +3787,10 @@
       <c r="J41">
         <v>0</v>
       </c>
-      <c r="K41" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L41" s="2">
+      <c r="K41" t="s">
+        <v>26</v>
+      </c>
+      <c r="L41" s="1">
         <v>45292</v>
       </c>
       <c r="M41">
@@ -3853,10 +3867,10 @@
       <c r="J42">
         <v>0</v>
       </c>
-      <c r="K42" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L42" s="2">
+      <c r="K42" t="s">
+        <v>26</v>
+      </c>
+      <c r="L42" s="1">
         <v>45292</v>
       </c>
       <c r="M42">
@@ -3933,10 +3947,10 @@
       <c r="J43">
         <v>0</v>
       </c>
-      <c r="K43" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L43" s="2">
+      <c r="K43" t="s">
+        <v>26</v>
+      </c>
+      <c r="L43" s="1">
         <v>45292</v>
       </c>
       <c r="M43">
@@ -4013,10 +4027,10 @@
       <c r="J44">
         <v>0</v>
       </c>
-      <c r="K44" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L44" s="2">
+      <c r="K44" t="s">
+        <v>26</v>
+      </c>
+      <c r="L44" s="1">
         <v>45292</v>
       </c>
       <c r="M44">
@@ -4093,10 +4107,10 @@
       <c r="J45">
         <v>0</v>
       </c>
-      <c r="K45" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L45" s="2">
+      <c r="K45" t="s">
+        <v>26</v>
+      </c>
+      <c r="L45" s="1">
         <v>45292</v>
       </c>
       <c r="M45">
@@ -4173,10 +4187,10 @@
       <c r="J46">
         <v>0</v>
       </c>
-      <c r="K46" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L46" s="2">
+      <c r="K46" t="s">
+        <v>26</v>
+      </c>
+      <c r="L46" s="1">
         <v>45292</v>
       </c>
       <c r="M46">
@@ -4253,10 +4267,10 @@
       <c r="J47">
         <v>0</v>
       </c>
-      <c r="K47" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L47" s="2">
+      <c r="K47" t="s">
+        <v>26</v>
+      </c>
+      <c r="L47" s="1">
         <v>45292</v>
       </c>
       <c r="M47">
@@ -4333,10 +4347,10 @@
       <c r="J48">
         <v>0</v>
       </c>
-      <c r="K48" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L48" s="2">
+      <c r="K48" t="s">
+        <v>26</v>
+      </c>
+      <c r="L48" s="1">
         <v>45292</v>
       </c>
       <c r="M48">
@@ -4413,10 +4427,10 @@
       <c r="J49">
         <v>0</v>
       </c>
-      <c r="K49" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L49" s="2">
+      <c r="K49" t="s">
+        <v>26</v>
+      </c>
+      <c r="L49" s="1">
         <v>45292</v>
       </c>
       <c r="M49">
@@ -4493,10 +4507,10 @@
       <c r="J50">
         <v>0</v>
       </c>
-      <c r="K50" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L50" s="2">
+      <c r="K50" t="s">
+        <v>26</v>
+      </c>
+      <c r="L50" s="1">
         <v>45292</v>
       </c>
       <c r="M50">
@@ -4573,10 +4587,10 @@
       <c r="J51">
         <v>0</v>
       </c>
-      <c r="K51" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L51" s="2">
+      <c r="K51" t="s">
+        <v>26</v>
+      </c>
+      <c r="L51" s="1">
         <v>45292</v>
       </c>
       <c r="M51">
@@ -4653,10 +4667,10 @@
       <c r="J52">
         <v>0</v>
       </c>
-      <c r="K52" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L52" s="2">
+      <c r="K52" t="s">
+        <v>26</v>
+      </c>
+      <c r="L52" s="1">
         <v>45292</v>
       </c>
       <c r="M52">
@@ -4733,10 +4747,10 @@
       <c r="J53">
         <v>0</v>
       </c>
-      <c r="K53" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L53" s="2">
+      <c r="K53" t="s">
+        <v>26</v>
+      </c>
+      <c r="L53" s="1">
         <v>45292</v>
       </c>
       <c r="M53">
@@ -4813,10 +4827,10 @@
       <c r="J54">
         <v>0</v>
       </c>
-      <c r="K54" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L54" s="2">
+      <c r="K54" t="s">
+        <v>26</v>
+      </c>
+      <c r="L54" s="1">
         <v>45292</v>
       </c>
       <c r="M54">
@@ -4893,10 +4907,10 @@
       <c r="J55">
         <v>0</v>
       </c>
-      <c r="K55" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L55" s="2">
+      <c r="K55" t="s">
+        <v>26</v>
+      </c>
+      <c r="L55" s="1">
         <v>45292</v>
       </c>
       <c r="M55">
@@ -4973,10 +4987,10 @@
       <c r="J56">
         <v>0</v>
       </c>
-      <c r="K56" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L56" s="2">
+      <c r="K56" t="s">
+        <v>26</v>
+      </c>
+      <c r="L56" s="1">
         <v>45292</v>
       </c>
       <c r="M56">
@@ -5053,10 +5067,10 @@
       <c r="J57">
         <v>0</v>
       </c>
-      <c r="K57" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L57" s="2">
+      <c r="K57" t="s">
+        <v>26</v>
+      </c>
+      <c r="L57" s="1">
         <v>45292</v>
       </c>
       <c r="M57">
@@ -5133,10 +5147,10 @@
       <c r="J58">
         <v>0</v>
       </c>
-      <c r="K58" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L58" s="2">
+      <c r="K58" t="s">
+        <v>26</v>
+      </c>
+      <c r="L58" s="1">
         <v>45292</v>
       </c>
       <c r="M58">
@@ -5213,10 +5227,10 @@
       <c r="J59">
         <v>0</v>
       </c>
-      <c r="K59" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L59" s="2">
+      <c r="K59" t="s">
+        <v>26</v>
+      </c>
+      <c r="L59" s="1">
         <v>45292</v>
       </c>
       <c r="M59">
@@ -5293,10 +5307,10 @@
       <c r="J60">
         <v>0</v>
       </c>
-      <c r="K60" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L60" s="2">
+      <c r="K60" t="s">
+        <v>26</v>
+      </c>
+      <c r="L60" s="1">
         <v>45292</v>
       </c>
       <c r="M60">
@@ -5373,10 +5387,10 @@
       <c r="J61">
         <v>0</v>
       </c>
-      <c r="K61" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L61" s="2">
+      <c r="K61" t="s">
+        <v>26</v>
+      </c>
+      <c r="L61" s="1">
         <v>45292</v>
       </c>
       <c r="M61">
@@ -5453,10 +5467,10 @@
       <c r="J62">
         <v>0</v>
       </c>
-      <c r="K62" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L62" s="2">
+      <c r="K62" t="s">
+        <v>26</v>
+      </c>
+      <c r="L62" s="1">
         <v>45292</v>
       </c>
       <c r="M62">
@@ -5533,10 +5547,10 @@
       <c r="J63">
         <v>0</v>
       </c>
-      <c r="K63" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L63" s="2">
+      <c r="K63" t="s">
+        <v>26</v>
+      </c>
+      <c r="L63" s="1">
         <v>45292</v>
       </c>
       <c r="M63">
@@ -5613,10 +5627,10 @@
       <c r="J64">
         <v>0</v>
       </c>
-      <c r="K64" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L64" s="2">
+      <c r="K64" t="s">
+        <v>26</v>
+      </c>
+      <c r="L64" s="1">
         <v>45292</v>
       </c>
       <c r="M64">
@@ -5693,10 +5707,10 @@
       <c r="J65">
         <v>0</v>
       </c>
-      <c r="K65" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L65" s="2">
+      <c r="K65" t="s">
+        <v>26</v>
+      </c>
+      <c r="L65" s="1">
         <v>45292</v>
       </c>
       <c r="M65">
@@ -5773,10 +5787,10 @@
       <c r="J66">
         <v>0</v>
       </c>
-      <c r="K66" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L66" s="2">
+      <c r="K66" t="s">
+        <v>26</v>
+      </c>
+      <c r="L66" s="1">
         <v>45292</v>
       </c>
       <c r="M66">
@@ -5853,10 +5867,10 @@
       <c r="J67">
         <v>0</v>
       </c>
-      <c r="K67" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L67" s="2">
+      <c r="K67" t="s">
+        <v>26</v>
+      </c>
+      <c r="L67" s="1">
         <v>45292</v>
       </c>
       <c r="M67">
@@ -5933,10 +5947,10 @@
       <c r="J68">
         <v>0</v>
       </c>
-      <c r="K68" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L68" s="2">
+      <c r="K68" t="s">
+        <v>26</v>
+      </c>
+      <c r="L68" s="1">
         <v>45292</v>
       </c>
       <c r="M68">
@@ -6013,10 +6027,10 @@
       <c r="J69">
         <v>0</v>
       </c>
-      <c r="K69" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L69" s="2">
+      <c r="K69" t="s">
+        <v>26</v>
+      </c>
+      <c r="L69" s="1">
         <v>45292</v>
       </c>
       <c r="M69">
@@ -6093,10 +6107,10 @@
       <c r="J70">
         <v>0</v>
       </c>
-      <c r="K70" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L70" s="2">
+      <c r="K70" t="s">
+        <v>26</v>
+      </c>
+      <c r="L70" s="1">
         <v>45292</v>
       </c>
       <c r="M70">
@@ -6173,10 +6187,10 @@
       <c r="J71">
         <v>0</v>
       </c>
-      <c r="K71" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L71" s="2">
+      <c r="K71" t="s">
+        <v>26</v>
+      </c>
+      <c r="L71" s="1">
         <v>45292</v>
       </c>
       <c r="M71">
@@ -6253,10 +6267,10 @@
       <c r="J72">
         <v>0</v>
       </c>
-      <c r="K72" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L72" s="2">
+      <c r="K72" t="s">
+        <v>26</v>
+      </c>
+      <c r="L72" s="1">
         <v>45292</v>
       </c>
       <c r="M72">
@@ -6333,10 +6347,10 @@
       <c r="J73">
         <v>0</v>
       </c>
-      <c r="K73" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L73" s="2">
+      <c r="K73" t="s">
+        <v>26</v>
+      </c>
+      <c r="L73" s="1">
         <v>45292</v>
       </c>
       <c r="M73">
@@ -6413,10 +6427,10 @@
       <c r="J74">
         <v>0</v>
       </c>
-      <c r="K74" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L74" s="2">
+      <c r="K74" t="s">
+        <v>26</v>
+      </c>
+      <c r="L74" s="1">
         <v>45292</v>
       </c>
       <c r="M74">
@@ -6493,10 +6507,10 @@
       <c r="J75">
         <v>0</v>
       </c>
-      <c r="K75" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L75" s="2">
+      <c r="K75" t="s">
+        <v>26</v>
+      </c>
+      <c r="L75" s="1">
         <v>45292</v>
       </c>
       <c r="M75">
@@ -6573,10 +6587,10 @@
       <c r="J76">
         <v>0</v>
       </c>
-      <c r="K76" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L76" s="2">
+      <c r="K76" t="s">
+        <v>26</v>
+      </c>
+      <c r="L76" s="1">
         <v>45292</v>
       </c>
       <c r="M76">
@@ -6653,10 +6667,10 @@
       <c r="J77">
         <v>0</v>
       </c>
-      <c r="K77" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L77" s="2">
+      <c r="K77" t="s">
+        <v>26</v>
+      </c>
+      <c r="L77" s="1">
         <v>45292</v>
       </c>
       <c r="M77">
@@ -6733,10 +6747,10 @@
       <c r="J78">
         <v>0</v>
       </c>
-      <c r="K78" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L78" s="2">
+      <c r="K78" t="s">
+        <v>26</v>
+      </c>
+      <c r="L78" s="1">
         <v>45292</v>
       </c>
       <c r="M78">
@@ -6813,10 +6827,10 @@
       <c r="J79">
         <v>0</v>
       </c>
-      <c r="K79" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L79" s="2">
+      <c r="K79" t="s">
+        <v>26</v>
+      </c>
+      <c r="L79" s="1">
         <v>45292</v>
       </c>
       <c r="M79">
@@ -6893,10 +6907,10 @@
       <c r="J80">
         <v>0</v>
       </c>
-      <c r="K80" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L80" s="2">
+      <c r="K80" t="s">
+        <v>26</v>
+      </c>
+      <c r="L80" s="1">
         <v>45292</v>
       </c>
       <c r="M80">
@@ -6973,10 +6987,10 @@
       <c r="J81">
         <v>0</v>
       </c>
-      <c r="K81" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L81" s="2">
+      <c r="K81" t="s">
+        <v>26</v>
+      </c>
+      <c r="L81" s="1">
         <v>45292</v>
       </c>
       <c r="M81">
@@ -7053,10 +7067,10 @@
       <c r="J82">
         <v>0</v>
       </c>
-      <c r="K82" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L82" s="2">
+      <c r="K82" t="s">
+        <v>26</v>
+      </c>
+      <c r="L82" s="1">
         <v>45292</v>
       </c>
       <c r="M82">
@@ -7133,10 +7147,10 @@
       <c r="J83">
         <v>0</v>
       </c>
-      <c r="K83" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L83" s="2">
+      <c r="K83" t="s">
+        <v>26</v>
+      </c>
+      <c r="L83" s="1">
         <v>45292</v>
       </c>
       <c r="M83">
@@ -7213,10 +7227,10 @@
       <c r="J84">
         <v>0</v>
       </c>
-      <c r="K84" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L84" s="2">
+      <c r="K84" t="s">
+        <v>26</v>
+      </c>
+      <c r="L84" s="1">
         <v>45292</v>
       </c>
       <c r="M84">
@@ -7293,10 +7307,10 @@
       <c r="J85">
         <v>0</v>
       </c>
-      <c r="K85" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L85" s="2">
+      <c r="K85" t="s">
+        <v>26</v>
+      </c>
+      <c r="L85" s="1">
         <v>45292</v>
       </c>
       <c r="M85">
@@ -7373,10 +7387,10 @@
       <c r="J86">
         <v>0</v>
       </c>
-      <c r="K86" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L86" s="2">
+      <c r="K86" t="s">
+        <v>26</v>
+      </c>
+      <c r="L86" s="1">
         <v>45292</v>
       </c>
       <c r="M86">
@@ -7453,10 +7467,10 @@
       <c r="J87">
         <v>0</v>
       </c>
-      <c r="K87" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L87" s="2">
+      <c r="K87" t="s">
+        <v>26</v>
+      </c>
+      <c r="L87" s="1">
         <v>45292</v>
       </c>
       <c r="M87">
@@ -7533,10 +7547,10 @@
       <c r="J88">
         <v>0</v>
       </c>
-      <c r="K88" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L88" s="2">
+      <c r="K88" t="s">
+        <v>26</v>
+      </c>
+      <c r="L88" s="1">
         <v>45292</v>
       </c>
       <c r="M88">
@@ -7613,10 +7627,10 @@
       <c r="J89">
         <v>0</v>
       </c>
-      <c r="K89" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L89" s="2">
+      <c r="K89" t="s">
+        <v>26</v>
+      </c>
+      <c r="L89" s="1">
         <v>45292</v>
       </c>
       <c r="M89">
@@ -7693,10 +7707,10 @@
       <c r="J90">
         <v>0</v>
       </c>
-      <c r="K90" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L90" s="2">
+      <c r="K90" t="s">
+        <v>26</v>
+      </c>
+      <c r="L90" s="1">
         <v>45292</v>
       </c>
       <c r="M90">
@@ -7773,10 +7787,10 @@
       <c r="J91">
         <v>0</v>
       </c>
-      <c r="K91" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L91" s="2">
+      <c r="K91" t="s">
+        <v>26</v>
+      </c>
+      <c r="L91" s="1">
         <v>45292</v>
       </c>
       <c r="M91">
@@ -7853,10 +7867,10 @@
       <c r="J92">
         <v>0</v>
       </c>
-      <c r="K92" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L92" s="2">
+      <c r="K92" t="s">
+        <v>26</v>
+      </c>
+      <c r="L92" s="1">
         <v>45292</v>
       </c>
       <c r="M92">
@@ -7933,10 +7947,10 @@
       <c r="J93">
         <v>0</v>
       </c>
-      <c r="K93" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L93" s="2">
+      <c r="K93" t="s">
+        <v>26</v>
+      </c>
+      <c r="L93" s="1">
         <v>45292</v>
       </c>
       <c r="M93">
@@ -8013,10 +8027,10 @@
       <c r="J94">
         <v>0</v>
       </c>
-      <c r="K94" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L94" s="2">
+      <c r="K94" t="s">
+        <v>26</v>
+      </c>
+      <c r="L94" s="1">
         <v>45292</v>
       </c>
       <c r="M94">
@@ -8093,10 +8107,10 @@
       <c r="J95">
         <v>0</v>
       </c>
-      <c r="K95" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L95" s="2">
+      <c r="K95" t="s">
+        <v>26</v>
+      </c>
+      <c r="L95" s="1">
         <v>45292</v>
       </c>
       <c r="M95">
@@ -8173,10 +8187,10 @@
       <c r="J96">
         <v>0</v>
       </c>
-      <c r="K96" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L96" s="2">
+      <c r="K96" t="s">
+        <v>26</v>
+      </c>
+      <c r="L96" s="1">
         <v>45292</v>
       </c>
       <c r="M96">
@@ -8253,10 +8267,10 @@
       <c r="J97">
         <v>0</v>
       </c>
-      <c r="K97" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L97" s="2">
+      <c r="K97" t="s">
+        <v>26</v>
+      </c>
+      <c r="L97" s="1">
         <v>45292</v>
       </c>
       <c r="M97">
@@ -8333,10 +8347,10 @@
       <c r="J98">
         <v>0</v>
       </c>
-      <c r="K98" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L98" s="2">
+      <c r="K98" t="s">
+        <v>26</v>
+      </c>
+      <c r="L98" s="1">
         <v>45292</v>
       </c>
       <c r="M98">
@@ -8413,10 +8427,10 @@
       <c r="J99">
         <v>0</v>
       </c>
-      <c r="K99" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L99" s="2">
+      <c r="K99" t="s">
+        <v>26</v>
+      </c>
+      <c r="L99" s="1">
         <v>45292</v>
       </c>
       <c r="M99">
@@ -8493,10 +8507,10 @@
       <c r="J100">
         <v>0</v>
       </c>
-      <c r="K100" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L100" s="2">
+      <c r="K100" t="s">
+        <v>26</v>
+      </c>
+      <c r="L100" s="1">
         <v>45292</v>
       </c>
       <c r="M100">
@@ -8573,10 +8587,10 @@
       <c r="J101">
         <v>0</v>
       </c>
-      <c r="K101" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L101" s="2">
+      <c r="K101" t="s">
+        <v>26</v>
+      </c>
+      <c r="L101" s="1">
         <v>45292</v>
       </c>
       <c r="M101">
@@ -8653,10 +8667,10 @@
       <c r="J102">
         <v>0</v>
       </c>
-      <c r="K102" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L102" s="2">
+      <c r="K102" t="s">
+        <v>26</v>
+      </c>
+      <c r="L102" s="1">
         <v>45292</v>
       </c>
       <c r="M102">
@@ -8733,10 +8747,10 @@
       <c r="J103">
         <v>0</v>
       </c>
-      <c r="K103" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L103" s="2">
+      <c r="K103" t="s">
+        <v>26</v>
+      </c>
+      <c r="L103" s="1">
         <v>45292</v>
       </c>
       <c r="M103">
@@ -8813,10 +8827,10 @@
       <c r="J104">
         <v>0</v>
       </c>
-      <c r="K104" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L104" s="2">
+      <c r="K104" t="s">
+        <v>26</v>
+      </c>
+      <c r="L104" s="1">
         <v>45292</v>
       </c>
       <c r="M104">
@@ -8893,10 +8907,10 @@
       <c r="J105">
         <v>0</v>
       </c>
-      <c r="K105" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L105" s="2">
+      <c r="K105" t="s">
+        <v>26</v>
+      </c>
+      <c r="L105" s="1">
         <v>45292</v>
       </c>
       <c r="M105">
@@ -8973,10 +8987,10 @@
       <c r="J106">
         <v>0</v>
       </c>
-      <c r="K106" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L106" s="2">
+      <c r="K106" t="s">
+        <v>26</v>
+      </c>
+      <c r="L106" s="1">
         <v>45292</v>
       </c>
       <c r="M106">
@@ -9053,10 +9067,10 @@
       <c r="J107">
         <v>0</v>
       </c>
-      <c r="K107" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L107" s="2">
+      <c r="K107" t="s">
+        <v>26</v>
+      </c>
+      <c r="L107" s="1">
         <v>45292</v>
       </c>
       <c r="M107">
@@ -9133,10 +9147,10 @@
       <c r="J108">
         <v>0</v>
       </c>
-      <c r="K108" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L108" s="2">
+      <c r="K108" t="s">
+        <v>26</v>
+      </c>
+      <c r="L108" s="1">
         <v>45292</v>
       </c>
       <c r="M108">
@@ -9213,10 +9227,10 @@
       <c r="J109">
         <v>0</v>
       </c>
-      <c r="K109" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L109" s="2">
+      <c r="K109" t="s">
+        <v>26</v>
+      </c>
+      <c r="L109" s="1">
         <v>45292</v>
       </c>
       <c r="M109">
@@ -9272,9 +9286,60 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>42.09</v>
+      </c>
+      <c r="B1">
+        <v>147.16</v>
+      </c>
+      <c r="C1">
+        <v>204.01</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>50.99</v>
+      </c>
+      <c r="B2">
+        <v>314.48</v>
+      </c>
+      <c r="C2">
+        <v>237.93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <f>A2-A1</f>
+        <v>8.8999999999999986</v>
+      </c>
+      <c r="B3">
+        <f t="shared" ref="B3:C3" si="0">B2-B1</f>
+        <v>167.32000000000002</v>
+      </c>
+      <c r="C3">
+        <f t="shared" si="0"/>
+        <v>33.920000000000016</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <f>A3/A2*100</f>
+        <v>17.45440282408315</v>
+      </c>
+      <c r="B4">
+        <f t="shared" ref="B4:C4" si="1">B3/B2*100</f>
+        <v>53.205291274484864</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="1"/>
+        <v>14.256293867944358</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
